--- a/artfynd/A 40309-2024 artfynd.xlsx
+++ b/artfynd/A 40309-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119891865</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40309-2024 artfynd.xlsx
+++ b/artfynd/A 40309-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119891865</v>
+        <v>119893803</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>738</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532457</v>
+        <v>532414</v>
       </c>
       <c r="R2" t="n">
-        <v>6459399</v>
+        <v>6459381</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,15 +758,16 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,6 +783,224 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119894124</v>
+      </c>
+      <c r="B3" t="n">
+        <v>81025</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>738</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Smacka, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>532452</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6459406</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120814728</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smacka, Smacka, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532419</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459370</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena  Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helena  Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40309-2024 artfynd.xlsx
+++ b/artfynd/A 40309-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893803</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120814728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>